--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_biobio.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_biobio.xlsx
@@ -391,10 +391,10 @@
         <v>163.0928695205699</v>
       </c>
       <c r="C2">
-        <v>13.76577595384609</v>
+        <v>13.76577595384608</v>
       </c>
       <c r="D2">
-        <v>63.78322503125373</v>
+        <v>63.78322503125372</v>
       </c>
       <c r="E2">
         <v>22.45099901490019</v>
@@ -451,7 +451,7 @@
         <v>14.90525054303049</v>
       </c>
       <c r="D5">
-        <v>57.45637030934012</v>
+        <v>57.45637030934013</v>
       </c>
       <c r="E5">
         <v>27.63837914762939</v>
@@ -530,7 +530,7 @@
         <v>64.30984642531794</v>
       </c>
       <c r="E9">
-        <v>17.00224515999455</v>
+        <v>17.00224515999454</v>
       </c>
     </row>
     <row r="10">
@@ -562,7 +562,7 @@
         <v>164.6730114380512</v>
       </c>
       <c r="C11">
-        <v>15.2692415374565</v>
+        <v>15.26924153745651</v>
       </c>
       <c r="D11">
         <v>59.58643859906409</v>
@@ -581,7 +581,7 @@
         <v>166.6776279732544</v>
       </c>
       <c r="C12">
-        <v>15.07709596919467</v>
+        <v>15.07709596919466</v>
       </c>
       <c r="D12">
         <v>59.79275810210051</v>
@@ -600,7 +600,7 @@
         <v>164.3892490348896</v>
       </c>
       <c r="C13">
-        <v>14.10909913057776</v>
+        <v>14.10909913057777</v>
       </c>
       <c r="D13">
         <v>62.6970587630773</v>
@@ -622,7 +622,7 @@
         <v>17.77507733097658</v>
       </c>
       <c r="D14">
-        <v>61.71380173810576</v>
+        <v>61.71380173810575</v>
       </c>
       <c r="E14">
         <v>20.51112093091766</v>
@@ -676,7 +676,7 @@
         <v>152.1100917431193</v>
       </c>
       <c r="C17">
-        <v>15.20647321428571</v>
+        <v>15.20647321428572</v>
       </c>
       <c r="D17">
         <v>61.66294642857143</v>
@@ -698,10 +698,10 @@
         <v>16.45212632284366</v>
       </c>
       <c r="D18">
-        <v>61.7206042498534</v>
+        <v>61.72060424985341</v>
       </c>
       <c r="E18">
-        <v>21.82726942730293</v>
+        <v>21.82726942730294</v>
       </c>
     </row>
     <row r="19">
@@ -717,7 +717,7 @@
         <v>18.72632853070946</v>
       </c>
       <c r="D19">
-        <v>62.53953379407286</v>
+        <v>62.53953379407285</v>
       </c>
       <c r="E19">
         <v>18.73413767521768</v>
@@ -774,7 +774,7 @@
         <v>14.54356846473029</v>
       </c>
       <c r="D22">
-        <v>57.78008298755186</v>
+        <v>57.78008298755187</v>
       </c>
       <c r="E22">
         <v>27.67634854771784</v>
@@ -815,7 +815,7 @@
         <v>60.45827763987015</v>
       </c>
       <c r="E24">
-        <v>23.3950735153714</v>
+        <v>23.39507351537139</v>
       </c>
     </row>
     <row r="25">
@@ -831,10 +831,10 @@
         <v>15.93654667480171</v>
       </c>
       <c r="D25">
-        <v>61.2751677852349</v>
+        <v>61.27516778523491</v>
       </c>
       <c r="E25">
-        <v>22.78828553996339</v>
+        <v>22.7882855399634</v>
       </c>
     </row>
     <row r="26">
@@ -926,7 +926,7 @@
         <v>13.88329979879276</v>
       </c>
       <c r="D30">
-        <v>58.90342052313883</v>
+        <v>58.90342052313884</v>
       </c>
       <c r="E30">
         <v>27.21327967806841</v>
@@ -964,7 +964,7 @@
         <v>15.52728902835369</v>
       </c>
       <c r="D32">
-        <v>60.17594979267063</v>
+        <v>60.17594979267062</v>
       </c>
       <c r="E32">
         <v>24.29676117897568</v>
@@ -1005,7 +1005,7 @@
         <v>63.99749373433584</v>
       </c>
       <c r="E34">
-        <v>14.08521303258145</v>
+        <v>14.08521303258146</v>
       </c>
     </row>
   </sheetData>
